--- a/Plans/Master Sheet.xlsx
+++ b/Plans/Master Sheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\colma\Documents\.School\Term 6\Engineering Project 5\Week 8\Project 3\EngPrg3\Plans\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD533D8F-0EC6-4B5C-8726-AF06D0A51E23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62319A2C-B080-42AD-B497-53EE6B80735F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1900" yWindow="1900" windowWidth="19200" windowHeight="11170" activeTab="2" xr2:uid="{4E248F06-6290-4F99-8284-0F58B4C0D068}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{4E248F06-6290-4F99-8284-0F58B4C0D068}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM" sheetId="4" r:id="rId1"/>
@@ -693,6 +693,7 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -714,7 +715,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1050,21 +1050,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{009B395D-6ABA-4638-8C6A-092975E4B5AC}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.08984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.54296875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.36328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.54296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>55</v>
       </c>
@@ -1096,7 +1096,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>81</v>
       </c>
@@ -1132,7 +1132,7 @@
         <v>103.02799999999995</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>66</v>
       </c>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="I3" s="6"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>67</v>
       </c>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="I4" s="6"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>68</v>
       </c>
@@ -1219,7 +1219,7 @@
       </c>
       <c r="I5" s="6"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>69</v>
       </c>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="I6" s="6"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>70</v>
       </c>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="I7" s="6"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>71</v>
       </c>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="I8" s="6"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>72</v>
       </c>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="I9" s="6"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>73</v>
       </c>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="I10" s="6"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>82</v>
       </c>
@@ -1401,79 +1401,79 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4601DC12-1E20-4EB1-95CA-36CE7ADD543C}">
   <dimension ref="A1:AB25"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.90625" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="8.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.90625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.90625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.81640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.90625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.08984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.26953125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.54296875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.26953125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="20.453125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7265625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.08984375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15.26953125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.7265625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="13" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="12.6328125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="21.81640625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.7265625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="8.36328125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="24" t="s">
+    <row r="1" spans="1:28" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="F1" s="24" t="s">
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="F1" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="G1" s="24"/>
+      <c r="G1" s="25"/>
       <c r="H1" s="3"/>
-      <c r="I1" s="24" t="s">
+      <c r="I1" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
-      <c r="L1" s="24"/>
-      <c r="M1" s="24"/>
-      <c r="N1" s="24"/>
-      <c r="O1" s="24"/>
-      <c r="P1" s="24"/>
-      <c r="Q1" s="24"/>
-      <c r="R1" s="24"/>
-      <c r="S1" s="24"/>
-      <c r="T1" s="24"/>
-      <c r="U1" s="24"/>
-      <c r="V1" s="24"/>
-      <c r="W1" s="24"/>
-      <c r="X1" s="24"/>
-      <c r="Y1" s="24"/>
-      <c r="Z1" s="24"/>
-      <c r="AA1" s="24"/>
-      <c r="AB1" s="24"/>
-    </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A2" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="25"/>
+      <c r="O1" s="25"/>
+      <c r="P1" s="25"/>
+      <c r="Q1" s="25"/>
+      <c r="R1" s="25"/>
+      <c r="S1" s="25"/>
+      <c r="T1" s="25"/>
+      <c r="U1" s="25"/>
+      <c r="V1" s="25"/>
+      <c r="W1" s="25"/>
+      <c r="X1" s="25"/>
+      <c r="Y1" s="25"/>
+      <c r="Z1" s="25"/>
+      <c r="AA1" s="25"/>
+      <c r="AB1" s="25"/>
+    </row>
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A2" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
       <c r="F2" s="1" t="s">
         <v>41</v>
       </c>
@@ -1541,13 +1541,13 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A3" s="25" t="s">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A3" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="25"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
       <c r="F3">
         <f>B9</f>
         <v>27.5</v>
@@ -1622,7 +1622,7 @@
         <v>18.707999999999998</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -1695,7 +1695,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -1771,7 +1771,7 @@
         <v>0.52800000000000002</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -1847,7 +1847,7 @@
         <v>8.7999999999999995E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -1926,7 +1926,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -2003,7 +2003,7 @@
         <v>0.185</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -2083,7 +2083,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -2161,7 +2161,7 @@
         <v>0.24749999999999997</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -2241,7 +2241,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
       <c r="F12" s="1" t="s">
         <v>47</v>
       </c>
@@ -2249,11 +2249,11 @@
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A13" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="B13" s="26"/>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A13" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" s="27"/>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
       <c r="F13">
@@ -2265,11 +2265,11 @@
         <v>1.2410000000000001</v>
       </c>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A14" s="25" t="s">
+    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A14" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="25"/>
+      <c r="B14" s="26"/>
       <c r="F14" s="1" t="s">
         <v>50</v>
       </c>
@@ -2277,7 +2277,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>10</v>
       </c>
@@ -2294,7 +2294,7 @@
         <v>-0.11600000000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>11</v>
       </c>
@@ -2308,7 +2308,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>12</v>
       </c>
@@ -2324,7 +2324,7 @@
         <v>1.125</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>13</v>
       </c>
@@ -2332,7 +2332,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>14</v>
       </c>
@@ -2340,7 +2340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>15</v>
       </c>
@@ -2349,7 +2349,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>16</v>
       </c>
@@ -2358,7 +2358,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>17</v>
       </c>
@@ -2367,21 +2367,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A24" s="22" t="s">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="23" t="s">
         <v>83</v>
       </c>
-      <c r="B24" s="22"/>
-      <c r="C24" s="22"/>
-      <c r="D24" s="22"/>
-    </row>
-    <row r="25" spans="1:7" ht="72.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="23" t="s">
+      <c r="B24" s="23"/>
+      <c r="C24" s="23"/>
+      <c r="D24" s="23"/>
+    </row>
+    <row r="25" spans="1:7" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="B25" s="23"/>
-      <c r="C25" s="23"/>
-      <c r="D25" s="23"/>
+      <c r="B25" s="24"/>
+      <c r="C25" s="24"/>
+      <c r="D25" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -2402,17 +2402,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82558BB8-CB08-42DC-96D6-45D81DA36A28}">
   <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.6328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.6328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>149</v>
       </c>
@@ -2432,7 +2432,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -2452,7 +2452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>58</v>
       </c>
@@ -2472,27 +2472,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
       <c r="B4">
         <v>12</v>
       </c>
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="22" t="s">
         <v>134</v>
       </c>
-      <c r="D4" s="29" t="s">
+      <c r="D4" s="22" t="s">
         <v>134</v>
       </c>
-      <c r="E4" s="29">
+      <c r="E4" s="22">
         <v>12</v>
       </c>
-      <c r="F4" s="29" t="s">
+      <c r="F4" s="22" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2512,14 +2512,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>22</v>
       </c>
       <c r="B6">
         <v>12</v>
       </c>
-      <c r="C6" s="29" t="s">
+      <c r="C6" s="22" t="s">
         <v>134</v>
       </c>
       <c r="D6">
@@ -2532,7 +2532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -2552,14 +2552,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>30</v>
       </c>
       <c r="B8">
         <v>12</v>
       </c>
-      <c r="C8" s="29" t="s">
+      <c r="C8" s="22" t="s">
         <v>134</v>
       </c>
       <c r="D8">
@@ -2572,7 +2572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>32</v>
       </c>
@@ -2592,7 +2592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>156</v>
       </c>
@@ -2621,7 +2621,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52C8AFA0-8489-4B36-9494-E5F50A15BF79}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2630,43 +2630,43 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A43CCE5A-C8B1-4FC0-987A-44B3BDE8779D}">
   <dimension ref="A1:R21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A1" s="27" t="s">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A1" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A2" s="22"/>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="25" t="s">
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="23"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="26" t="s">
         <v>147</v>
       </c>
-      <c r="E2" s="25"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="K2" s="22"/>
-      <c r="L2" s="22"/>
-      <c r="M2" s="22"/>
-      <c r="N2" s="25" t="s">
+      <c r="E2" s="26"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="23"/>
+      <c r="M2" s="23"/>
+      <c r="N2" s="26" t="s">
         <v>148</v>
       </c>
-      <c r="O2" s="25"/>
-      <c r="P2" s="22"/>
-      <c r="Q2" s="22"/>
-      <c r="R2" s="22"/>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="O2" s="26"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23"/>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>102</v>
       </c>
@@ -2716,7 +2716,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>139</v>
       </c>
@@ -2762,7 +2762,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
         <v>138</v>
       </c>
@@ -2808,7 +2808,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>134</v>
       </c>
@@ -2854,7 +2854,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>134</v>
       </c>
@@ -2900,7 +2900,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>127</v>
       </c>
@@ -2946,7 +2946,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
         <v>134</v>
       </c>
@@ -2992,7 +2992,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>118</v>
       </c>
@@ -3038,7 +3038,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
         <v>121</v>
       </c>
@@ -3084,7 +3084,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="D12" s="12">
         <v>9</v>
       </c>
@@ -3098,7 +3098,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="D13" s="12">
         <v>10</v>
       </c>
@@ -3112,7 +3112,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="D14" s="12">
         <v>11</v>
       </c>
@@ -3126,7 +3126,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="D15" s="12">
         <v>12</v>
       </c>
@@ -3140,7 +3140,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="D16" s="12">
         <v>13</v>
       </c>
@@ -3154,7 +3154,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="4:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="4:15" x14ac:dyDescent="0.25">
       <c r="D17" s="12">
         <v>14</v>
       </c>
@@ -3168,7 +3168,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="4:15" x14ac:dyDescent="0.35">
+    <row r="18" spans="4:15" x14ac:dyDescent="0.25">
       <c r="D18" s="12">
         <v>15</v>
       </c>
@@ -3182,7 +3182,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="4:15" x14ac:dyDescent="0.35">
+    <row r="19" spans="4:15" x14ac:dyDescent="0.25">
       <c r="D19" s="12">
         <v>16</v>
       </c>
@@ -3196,7 +3196,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="4:15" x14ac:dyDescent="0.35">
+    <row r="20" spans="4:15" x14ac:dyDescent="0.25">
       <c r="D20" s="12">
         <v>17</v>
       </c>
@@ -3210,7 +3210,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="4:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="4:15" x14ac:dyDescent="0.25">
       <c r="D21" s="12">
         <v>18</v>
       </c>
@@ -3241,30 +3241,30 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8DB7992-C396-4C4D-AF9E-415D6DF99652}">
   <dimension ref="A1:H10"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.36328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="3.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.26953125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A1" s="27" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>102</v>
       </c>
@@ -3290,7 +3290,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>118</v>
       </c>
@@ -3314,7 +3314,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>121</v>
       </c>
@@ -3336,7 +3336,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
         <v>119</v>
       </c>
@@ -3362,14 +3362,14 @@
         <v>120</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" s="28" t="s">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="29" t="s">
         <v>106</v>
       </c>
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="29" t="s">
         <v>112</v>
       </c>
-      <c r="C6" s="28" t="s">
+      <c r="C6" s="29" t="s">
         <v>86</v>
       </c>
       <c r="D6" s="12">
@@ -3378,31 +3378,31 @@
       <c r="E6" s="12">
         <v>13</v>
       </c>
-      <c r="F6" s="27" t="s">
+      <c r="F6" s="28" t="s">
         <v>86</v>
       </c>
-      <c r="G6" s="28" t="s">
+      <c r="G6" s="29" t="s">
         <v>112</v>
       </c>
-      <c r="H6" s="28" t="s">
+      <c r="H6" s="29" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A7" s="28"/>
-      <c r="B7" s="28"/>
-      <c r="C7" s="28"/>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="29"/>
+      <c r="B7" s="29"/>
+      <c r="C7" s="29"/>
       <c r="D7" s="12">
         <v>5</v>
       </c>
       <c r="E7" s="12">
         <v>12</v>
       </c>
-      <c r="F7" s="27"/>
-      <c r="G7" s="28"/>
-      <c r="H7" s="28"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F7" s="28"/>
+      <c r="G7" s="29"/>
+      <c r="H7" s="29"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>119</v>
       </c>
@@ -3428,7 +3428,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
         <v>121</v>
       </c>
@@ -3450,7 +3450,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>136</v>
       </c>
@@ -3491,25 +3491,25 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CC99365-AE94-4DBF-BA99-AE4F033C811D}">
   <dimension ref="A1:H10"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="6" max="6" width="10.36328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A1" s="27" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>102</v>
       </c>
@@ -3535,7 +3535,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>139</v>
       </c>
@@ -3559,7 +3559,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>138</v>
       </c>
@@ -3583,7 +3583,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
         <v>134</v>
       </c>
@@ -3607,7 +3607,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>134</v>
       </c>
@@ -3631,7 +3631,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>127</v>
       </c>
@@ -3655,7 +3655,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>134</v>
       </c>
@@ -3679,7 +3679,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
         <v>118</v>
       </c>
@@ -3703,7 +3703,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>121</v>
       </c>
@@ -3738,28 +3738,28 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14BA7CFB-DC85-4F03-86C5-E3FB28A80C68}">
   <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="10.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.90625" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="3.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.90625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A1" s="25" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>102</v>
       </c>
@@ -3785,8 +3785,8 @@
         <v>102</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" s="25"/>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="26"/>
       <c r="B3" s="5"/>
       <c r="C3" s="5" t="s">
         <v>88</v>
@@ -3801,10 +3801,10 @@
         <v>101</v>
       </c>
       <c r="G3" s="5"/>
-      <c r="H3" s="25"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" s="25"/>
+      <c r="H3" s="26"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="26"/>
       <c r="B4" s="5"/>
       <c r="C4" s="8" t="s">
         <v>94</v>
@@ -3819,10 +3819,10 @@
         <v>100</v>
       </c>
       <c r="G4" s="5"/>
-      <c r="H4" s="25"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5" s="25"/>
+      <c r="H4" s="26"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="26"/>
       <c r="B5" s="5"/>
       <c r="C5" s="8" t="s">
         <v>93</v>
@@ -3837,9 +3837,9 @@
         <v>99</v>
       </c>
       <c r="G5" s="5"/>
-      <c r="H5" s="25"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H5" s="26"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>106</v>
       </c>
@@ -3865,8 +3865,8 @@
         <v>103</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A7" s="25"/>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="26"/>
       <c r="B7" s="5"/>
       <c r="C7" s="8" t="s">
         <v>91</v>
@@ -3881,10 +3881,10 @@
         <v>98</v>
       </c>
       <c r="G7" s="5"/>
-      <c r="H7" s="25"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A8" s="25"/>
+      <c r="H7" s="26"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="26"/>
       <c r="B8" s="5"/>
       <c r="C8" s="8" t="s">
         <v>92</v>
@@ -3899,10 +3899,10 @@
         <v>97</v>
       </c>
       <c r="G8" s="5"/>
-      <c r="H8" s="25"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A9" s="25"/>
+      <c r="H8" s="26"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="26"/>
       <c r="B9" s="5"/>
       <c r="C9" s="5" t="s">
         <v>89</v>
@@ -3917,7 +3917,7 @@
         <v>90</v>
       </c>
       <c r="G9" s="5"/>
-      <c r="H9" s="25"/>
+      <c r="H9" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/Plans/Master Sheet.xlsx
+++ b/Plans/Master Sheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\colma\Documents\.School\Term 6\Engineering Project 5\Week 8\Project 3\EngPrg3\Plans\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62319A2C-B080-42AD-B497-53EE6B80735F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E465BBEE-BEBA-46B2-84B2-C2226670A101}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{4E248F06-6290-4F99-8284-0F58B4C0D068}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="4" xr2:uid="{4E248F06-6290-4F99-8284-0F58B4C0D068}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM" sheetId="4" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="278">
   <si>
     <t>Device</t>
   </si>
@@ -536,6 +536,369 @@
   </si>
   <si>
     <t>Encoder</t>
+  </si>
+  <si>
+    <t>I2C1_SCL</t>
+  </si>
+  <si>
+    <t>SPI1_SCLK</t>
+  </si>
+  <si>
+    <t>SPI1_PICO</t>
+  </si>
+  <si>
+    <t>SPI1_POCI</t>
+  </si>
+  <si>
+    <t>I2C_SDA</t>
+  </si>
+  <si>
+    <t>AnalogIn</t>
+  </si>
+  <si>
+    <t>PWM1/2</t>
+  </si>
+  <si>
+    <t>PWM1/1</t>
+  </si>
+  <si>
+    <t>PWM1/3</t>
+  </si>
+  <si>
+    <t>PWM1/4</t>
+  </si>
+  <si>
+    <t>PB_2</t>
+  </si>
+  <si>
+    <t>PB_1</t>
+  </si>
+  <si>
+    <t>PB_8</t>
+  </si>
+  <si>
+    <t>PB_9</t>
+  </si>
+  <si>
+    <t>PA_5</t>
+  </si>
+  <si>
+    <t>PA_6</t>
+  </si>
+  <si>
+    <t>PA_7</t>
+  </si>
+  <si>
+    <t>PB_0</t>
+  </si>
+  <si>
+    <t>PC_1</t>
+  </si>
+  <si>
+    <t>PC_0</t>
+  </si>
+  <si>
+    <t>PC_2</t>
+  </si>
+  <si>
+    <t>PC_3</t>
+  </si>
+  <si>
+    <t>PA_12</t>
+  </si>
+  <si>
+    <t>PA_11</t>
+  </si>
+  <si>
+    <t>PB_15</t>
+  </si>
+  <si>
+    <t>PB_14</t>
+  </si>
+  <si>
+    <t>PB_13</t>
+  </si>
+  <si>
+    <t>PB_12</t>
+  </si>
+  <si>
+    <t>PB_11</t>
+  </si>
+  <si>
+    <t>PB_10</t>
+  </si>
+  <si>
+    <t>PC_8</t>
+  </si>
+  <si>
+    <t>PC_6</t>
+  </si>
+  <si>
+    <t>PC_5</t>
+  </si>
+  <si>
+    <t>N/C</t>
+  </si>
+  <si>
+    <t>AGND</t>
+  </si>
+  <si>
+    <t>PC_4</t>
+  </si>
+  <si>
+    <t>AVDD</t>
+  </si>
+  <si>
+    <t>PA_9</t>
+  </si>
+  <si>
+    <t>PA_10</t>
+  </si>
+  <si>
+    <t>PA_13</t>
+  </si>
+  <si>
+    <t>PA_14</t>
+  </si>
+  <si>
+    <t>PA_15</t>
+  </si>
+  <si>
+    <t>PA_8</t>
+  </si>
+  <si>
+    <t>PB_4</t>
+  </si>
+  <si>
+    <t>PB_5</t>
+  </si>
+  <si>
+    <t>PB_3</t>
+  </si>
+  <si>
+    <t>PC_9</t>
+  </si>
+  <si>
+    <t>PB_6</t>
+  </si>
+  <si>
+    <t>PB_7</t>
+  </si>
+  <si>
+    <t>PC_7</t>
+  </si>
+  <si>
+    <t>PA_2</t>
+  </si>
+  <si>
+    <t>PA_3</t>
+  </si>
+  <si>
+    <t>PC_10</t>
+  </si>
+  <si>
+    <t>PC_12</t>
+  </si>
+  <si>
+    <t>VDD</t>
+  </si>
+  <si>
+    <t>BOOT0</t>
+  </si>
+  <si>
+    <t>PC_13</t>
+  </si>
+  <si>
+    <t>PC_14</t>
+  </si>
+  <si>
+    <t>PC_15</t>
+  </si>
+  <si>
+    <t>PF_0</t>
+  </si>
+  <si>
+    <t>PF_1</t>
+  </si>
+  <si>
+    <t>VBAT</t>
+  </si>
+  <si>
+    <t>PC_11</t>
+  </si>
+  <si>
+    <t>PD_2</t>
+  </si>
+  <si>
+    <t>E5V</t>
+  </si>
+  <si>
+    <t>IOREF</t>
+  </si>
+  <si>
+    <t>RESET</t>
+  </si>
+  <si>
+    <t>3V3</t>
+  </si>
+  <si>
+    <t>VIN</t>
+  </si>
+  <si>
+    <t>PA_0</t>
+  </si>
+  <si>
+    <t>PA_1</t>
+  </si>
+  <si>
+    <t>PA_4</t>
+  </si>
+  <si>
+    <t>DIR_X</t>
+  </si>
+  <si>
+    <t>STP_X</t>
+  </si>
+  <si>
+    <t>STP_Y</t>
+  </si>
+  <si>
+    <t>DIR_Y</t>
+  </si>
+  <si>
+    <t>MO1_Y</t>
+  </si>
+  <si>
+    <t>MO2_Y</t>
+  </si>
+  <si>
+    <t>MO0_Y</t>
+  </si>
+  <si>
+    <t>MO0_X</t>
+  </si>
+  <si>
+    <t>MO1_X</t>
+  </si>
+  <si>
+    <t>MO2_X</t>
+  </si>
+  <si>
+    <t>DIR_DC</t>
+  </si>
+  <si>
+    <t>SET_DC</t>
+  </si>
+  <si>
+    <t>FBK_DC</t>
+  </si>
+  <si>
+    <t>SPI_CE</t>
+  </si>
+  <si>
+    <t>SPI_IRQ</t>
+  </si>
+  <si>
+    <t>LIM_F</t>
+  </si>
+  <si>
+    <t>LIM_R</t>
+  </si>
+  <si>
+    <t>SW_U</t>
+  </si>
+  <si>
+    <t>POT_U</t>
+  </si>
+  <si>
+    <t>BUT_U</t>
+  </si>
+  <si>
+    <t>BUZ_U</t>
+  </si>
+  <si>
+    <t>XCVR_CLK</t>
+  </si>
+  <si>
+    <t>XCVR_TX</t>
+  </si>
+  <si>
+    <t>XCVR_RX</t>
+  </si>
+  <si>
+    <t>OLED_CLK</t>
+  </si>
+  <si>
+    <t>OLED_DAT</t>
+  </si>
+  <si>
+    <t>QEN_A</t>
+  </si>
+  <si>
+    <t>QEN_B</t>
+  </si>
+  <si>
+    <t>DIG_OUT</t>
+  </si>
+  <si>
+    <t>DIG_IN</t>
+  </si>
+  <si>
+    <t>5V_IN</t>
+  </si>
+  <si>
+    <t>3V3_OUT</t>
+  </si>
+  <si>
+    <t>5V_OUT</t>
+  </si>
+  <si>
+    <t>BOOT</t>
+  </si>
+  <si>
+    <t>SLP_Y</t>
+  </si>
+  <si>
+    <t>RST_Y</t>
+  </si>
+  <si>
+    <t>EN_Y</t>
+  </si>
+  <si>
+    <t>SLP_X</t>
+  </si>
+  <si>
+    <t>RST_X</t>
+  </si>
+  <si>
+    <t>EN_X</t>
+  </si>
+  <si>
+    <t>SET_VIB</t>
+  </si>
+  <si>
+    <t>RST_BUT</t>
+  </si>
+  <si>
+    <t>BOOT_BUT</t>
+  </si>
+  <si>
+    <t>SER1_TX</t>
+  </si>
+  <si>
+    <t>SER1_RX</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>14 Free Pins</t>
+  </si>
+  <si>
+    <t>TIM2_CH1</t>
+  </si>
+  <si>
+    <t>TIM2_CH2</t>
   </si>
 </sst>
 </file>
@@ -570,7 +933,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -625,6 +988,30 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.749992370372631"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -638,7 +1025,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -694,6 +1081,24 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" quotePrefix="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -709,11 +1114,17 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -721,6 +1132,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFFFFCC"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1433,47 +1849,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="F1" s="25" t="s">
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="F1" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="G1" s="25"/>
+      <c r="G1" s="31"/>
       <c r="H1" s="3"/>
-      <c r="I1" s="25" t="s">
+      <c r="I1" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="25"/>
-      <c r="O1" s="25"/>
-      <c r="P1" s="25"/>
-      <c r="Q1" s="25"/>
-      <c r="R1" s="25"/>
-      <c r="S1" s="25"/>
-      <c r="T1" s="25"/>
-      <c r="U1" s="25"/>
-      <c r="V1" s="25"/>
-      <c r="W1" s="25"/>
-      <c r="X1" s="25"/>
-      <c r="Y1" s="25"/>
-      <c r="Z1" s="25"/>
-      <c r="AA1" s="25"/>
-      <c r="AB1" s="25"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
+      <c r="M1" s="31"/>
+      <c r="N1" s="31"/>
+      <c r="O1" s="31"/>
+      <c r="P1" s="31"/>
+      <c r="Q1" s="31"/>
+      <c r="R1" s="31"/>
+      <c r="S1" s="31"/>
+      <c r="T1" s="31"/>
+      <c r="U1" s="31"/>
+      <c r="V1" s="31"/>
+      <c r="W1" s="31"/>
+      <c r="X1" s="31"/>
+      <c r="Y1" s="31"/>
+      <c r="Z1" s="31"/>
+      <c r="AA1" s="31"/>
+      <c r="AB1" s="31"/>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
       <c r="F2" s="1" t="s">
         <v>41</v>
       </c>
@@ -1542,12 +1958,12 @@
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A3" s="26" t="s">
+      <c r="A3" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
       <c r="F3">
         <f>B9</f>
         <v>27.5</v>
@@ -2250,10 +2666,10 @@
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A13" s="27" t="s">
+      <c r="A13" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B13" s="27"/>
+      <c r="B13" s="33"/>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
       <c r="F13">
@@ -2266,10 +2682,10 @@
       </c>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A14" s="26" t="s">
+      <c r="A14" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="26"/>
+      <c r="B14" s="32"/>
       <c r="F14" s="1" t="s">
         <v>50</v>
       </c>
@@ -2368,20 +2784,20 @@
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="23" t="s">
+      <c r="A24" s="29" t="s">
         <v>83</v>
       </c>
-      <c r="B24" s="23"/>
-      <c r="C24" s="23"/>
-      <c r="D24" s="23"/>
+      <c r="B24" s="29"/>
+      <c r="C24" s="29"/>
+      <c r="D24" s="29"/>
     </row>
     <row r="25" spans="1:7" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="24" t="s">
+      <c r="A25" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="B25" s="24"/>
-      <c r="C25" s="24"/>
-      <c r="D25" s="24"/>
+      <c r="B25" s="30"/>
+      <c r="C25" s="30"/>
+      <c r="D25" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -2629,610 +3045,1091 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A43CCE5A-C8B1-4FC0-987A-44B3BDE8779D}">
-  <dimension ref="A1:R21"/>
+  <dimension ref="A1:V27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5703125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A1" s="28" t="s">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A1" s="34" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A2" s="23"/>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="26" t="s">
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="34"/>
+      <c r="R1" s="34"/>
+      <c r="S1" s="34"/>
+      <c r="T1" s="34"/>
+      <c r="U1" s="34"/>
+      <c r="V1" s="34"/>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A2" s="7"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="32" t="s">
         <v>147</v>
       </c>
-      <c r="E2" s="26"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="23"/>
-      <c r="H2" s="23"/>
-      <c r="K2" s="23"/>
-      <c r="L2" s="23"/>
-      <c r="M2" s="23"/>
-      <c r="N2" s="26" t="s">
+      <c r="F2" s="32"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="7"/>
+      <c r="O2" s="7"/>
+      <c r="P2" s="7"/>
+      <c r="Q2" s="32" t="s">
         <v>148</v>
       </c>
-      <c r="O2" s="26"/>
-      <c r="P2" s="23"/>
-      <c r="Q2" s="23"/>
-      <c r="R2" s="23"/>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
+      <c r="R2" s="32"/>
+      <c r="S2" s="7"/>
+      <c r="T2" s="7"/>
+      <c r="U2" s="7"/>
+      <c r="V2" s="2"/>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="B3" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="C3" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="D3" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="E3" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="F3" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="G3" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="H3" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="I3" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="K3" s="10" t="s">
+      <c r="J3" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="M3" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="N3" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="L3" s="10" t="s">
+      <c r="O3" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="M3" s="10" t="s">
+      <c r="P3" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="N3" s="10" t="s">
+      <c r="Q3" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="O3" s="10" t="s">
+      <c r="R3" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="P3" s="10" t="s">
+      <c r="S3" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="Q3" s="10" t="s">
+      <c r="T3" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="R3" s="10" t="s">
+      <c r="U3" s="12" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="B4" s="16"/>
+      <c r="V3" s="12" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B4" s="9" t="s">
+        <v>230</v>
+      </c>
       <c r="C4" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="D4" s="12">
+        <v>209</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="E4" s="12">
         <v>1</v>
       </c>
-      <c r="E4" s="12">
+      <c r="F4" s="12">
+        <v>38</v>
+      </c>
+      <c r="G4" s="27"/>
+      <c r="H4" s="28" t="s">
+        <v>219</v>
+      </c>
+      <c r="I4" s="27"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
+      <c r="N4" s="28"/>
+      <c r="O4" s="28" t="s">
+        <v>203</v>
+      </c>
+      <c r="P4" s="28"/>
+      <c r="Q4" s="12">
+        <v>1</v>
+      </c>
+      <c r="R4" s="12">
+        <v>38</v>
+      </c>
+      <c r="S4" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="T4" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="U4" s="9" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B5" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="E5" s="12">
+        <v>3</v>
+      </c>
+      <c r="F5" s="12">
+        <v>37</v>
+      </c>
+      <c r="G5" s="27"/>
+      <c r="H5" s="28" t="s">
+        <v>220</v>
+      </c>
+      <c r="I5" s="27"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="N5" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="O5" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="P5" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="Q5" s="12">
+        <v>3</v>
+      </c>
+      <c r="R5" s="12">
+        <v>37</v>
+      </c>
+      <c r="S5" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="T5" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="U5" s="9" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B6" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="C6" s="23" t="s">
+        <v>211</v>
+      </c>
+      <c r="D6" s="23" t="s">
+        <v>211</v>
+      </c>
+      <c r="E6" s="12">
+        <v>5</v>
+      </c>
+      <c r="F6" s="12">
         <v>36</v>
       </c>
-      <c r="F4" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="K4" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="L4" s="16"/>
-      <c r="M4" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="N4" s="12">
-        <v>1</v>
-      </c>
-      <c r="O4" s="12">
+      <c r="G6" s="23" t="s">
+        <v>221</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="N6" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="O6" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="P6" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q6" s="12">
+        <v>5</v>
+      </c>
+      <c r="R6" s="12">
         <v>36</v>
       </c>
-      <c r="P4" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="Q4" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="R4" s="9" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="B5" s="17"/>
-      <c r="C5" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="D5" s="12">
-        <v>3</v>
-      </c>
-      <c r="E5" s="12">
+      <c r="S6" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="T6" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="U6" s="9" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B7" s="23" t="s">
+        <v>271</v>
+      </c>
+      <c r="C7" s="23" t="s">
+        <v>212</v>
+      </c>
+      <c r="D7" s="23" t="s">
+        <v>262</v>
+      </c>
+      <c r="E7" s="12">
+        <v>4</v>
+      </c>
+      <c r="F7" s="12">
         <v>35</v>
       </c>
-      <c r="F5" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="G5" s="9" t="s">
+      <c r="G7" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="H5" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="K5" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="L5" s="17"/>
-      <c r="M5" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="N5" s="12">
-        <v>3</v>
-      </c>
-      <c r="O5" s="12">
+      <c r="H7" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="I7" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5"/>
+      <c r="N7" s="23" t="s">
+        <v>259</v>
+      </c>
+      <c r="O7" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="P7" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="Q7" s="12">
+        <v>4</v>
+      </c>
+      <c r="R7" s="12">
         <v>35</v>
       </c>
-      <c r="P5" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="Q5" s="9" t="s">
+      <c r="S7" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="T7" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="U7" s="7" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B8" s="24" t="s">
+        <v>190</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>190</v>
+      </c>
+      <c r="D8" s="24" t="s">
+        <v>190</v>
+      </c>
+      <c r="E8" s="12">
+        <v>5</v>
+      </c>
+      <c r="F8" s="12">
+        <v>34</v>
+      </c>
+      <c r="G8" s="24" t="s">
+        <v>190</v>
+      </c>
+      <c r="H8" s="24" t="s">
+        <v>190</v>
+      </c>
+      <c r="I8" s="24" t="s">
+        <v>190</v>
+      </c>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="N8" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="R5" s="9" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="D6" s="12">
+      <c r="O8" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="P8" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q8" s="12">
         <v>5</v>
       </c>
-      <c r="E6" s="12">
+      <c r="R8" s="12">
         <v>34</v>
       </c>
-      <c r="F6" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="G6" s="19"/>
-      <c r="H6" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="K6" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="L6" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="M6" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="N6" s="12">
-        <v>5</v>
-      </c>
-      <c r="O6" s="12">
-        <v>34</v>
-      </c>
-      <c r="P6" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="Q6" s="19"/>
-      <c r="R6" s="9" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="D7" s="12">
-        <v>4</v>
-      </c>
-      <c r="E7" s="12">
+      <c r="S8" s="25" t="s">
+        <v>190</v>
+      </c>
+      <c r="T8" s="25" t="s">
+        <v>190</v>
+      </c>
+      <c r="U8" s="26" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B9" s="25" t="s">
+        <v>190</v>
+      </c>
+      <c r="C9" s="25" t="s">
+        <v>190</v>
+      </c>
+      <c r="D9" s="25" t="s">
+        <v>190</v>
+      </c>
+      <c r="E9" s="12">
+        <v>6</v>
+      </c>
+      <c r="F9" s="12">
         <v>33</v>
       </c>
-      <c r="F7" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="G7" s="20"/>
-      <c r="H7" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="K7" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="L7" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="M7" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="N7" s="12">
-        <v>4</v>
-      </c>
-      <c r="O7" s="12">
+      <c r="G9" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="I9" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
+      <c r="N9" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="O9" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="P9" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q9" s="12">
+        <v>6</v>
+      </c>
+      <c r="R9" s="12">
         <v>33</v>
       </c>
-      <c r="P7" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="Q7" s="20"/>
-      <c r="R7" s="11" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="B8" s="18"/>
-      <c r="C8" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="D8" s="12">
-        <v>5</v>
-      </c>
-      <c r="E8" s="12">
+      <c r="S9" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="T9" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="U9" s="9" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B10" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="E10" s="12">
+        <v>7</v>
+      </c>
+      <c r="F10" s="12">
         <v>32</v>
       </c>
-      <c r="F8" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="G8" s="20" t="s">
-        <v>146</v>
-      </c>
-      <c r="H8" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="K8" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="L8" s="18"/>
-      <c r="M8" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="N8" s="12">
-        <v>5</v>
-      </c>
-      <c r="O8" s="12">
+      <c r="G10" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="I10" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
+      <c r="N10" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="O10" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="P10" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q10" s="12">
+        <v>7</v>
+      </c>
+      <c r="R10" s="12">
         <v>32</v>
       </c>
-      <c r="P8" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="Q8" s="20" t="s">
-        <v>146</v>
-      </c>
-      <c r="R8" s="11" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="D9" s="12">
-        <v>6</v>
-      </c>
-      <c r="E9" s="12">
+      <c r="S10" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="T10" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="U10" s="9" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B11" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="E11" s="12">
+        <v>8</v>
+      </c>
+      <c r="F11" s="12">
         <v>31</v>
       </c>
-      <c r="F9" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="G9" s="19"/>
-      <c r="H9" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="K9" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="L9" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="M9" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="N9" s="12">
-        <v>6</v>
-      </c>
-      <c r="O9" s="12">
+      <c r="G11" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="H11" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="I11" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
+      <c r="N11" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="O11" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="P11" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q11" s="12">
+        <v>8</v>
+      </c>
+      <c r="R11" s="12">
         <v>31</v>
       </c>
-      <c r="P9" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="Q9" s="19"/>
-      <c r="R9" s="9" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="B10" s="21"/>
-      <c r="C10" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="D10" s="12">
-        <v>7</v>
-      </c>
-      <c r="E10" s="12">
+      <c r="S11" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="T11" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="U11" s="9" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B12" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="E12" s="12">
+        <v>9</v>
+      </c>
+      <c r="F12" s="12">
         <v>30</v>
       </c>
-      <c r="F10" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="G10" s="9" t="s">
+      <c r="G12" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="H10" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="K10" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="L10" s="21"/>
-      <c r="M10" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="N10" s="12">
-        <v>7</v>
-      </c>
-      <c r="O10" s="12">
+      <c r="H12" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5"/>
+      <c r="N12" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="O12" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="P12" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q12" s="12">
+        <v>9</v>
+      </c>
+      <c r="R12" s="12">
         <v>30</v>
       </c>
-      <c r="P10" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="Q10" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="R10" s="9" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="B11" s="14"/>
-      <c r="C11" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="D11" s="12">
-        <v>8</v>
-      </c>
-      <c r="E11" s="12">
+      <c r="S12" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="T12" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="U12" s="5" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B13" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="E13" s="12">
+        <v>10</v>
+      </c>
+      <c r="F13" s="12">
         <v>29</v>
       </c>
-      <c r="F11" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="G11" s="9" t="s">
+      <c r="G13" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="H11" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="K11" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="L11" s="14"/>
-      <c r="M11" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="N11" s="12">
-        <v>8</v>
-      </c>
-      <c r="O11" s="12">
+      <c r="H13" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
+      <c r="N13" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="O13" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="P13" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q13" s="12">
+        <v>10</v>
+      </c>
+      <c r="R13" s="12">
         <v>29</v>
       </c>
-      <c r="P11" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="Q11" s="9" t="s">
+      <c r="S13" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="R11" s="9" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="D12" s="12">
-        <v>9</v>
-      </c>
-      <c r="E12" s="12">
+      <c r="T13" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="U13" s="7" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B14" s="27"/>
+      <c r="C14" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="D14" s="27"/>
+      <c r="E14" s="12">
+        <v>11</v>
+      </c>
+      <c r="F14" s="12">
         <v>28</v>
       </c>
-      <c r="N12" s="12">
-        <v>9</v>
-      </c>
-      <c r="O12" s="12">
+      <c r="G14" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="N14" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="O14" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="P14" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q14" s="12">
+        <v>11</v>
+      </c>
+      <c r="R14" s="12">
         <v>28</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="D13" s="12">
-        <v>10</v>
-      </c>
-      <c r="E13" s="12">
+      <c r="S14" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="T14" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="U14" s="5" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B15" s="27"/>
+      <c r="C15" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="D15" s="27"/>
+      <c r="E15" s="12">
+        <v>12</v>
+      </c>
+      <c r="F15" s="12">
         <v>27</v>
       </c>
-      <c r="N13" s="12">
-        <v>10</v>
-      </c>
-      <c r="O13" s="12">
+      <c r="G15" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="J15" s="5"/>
+      <c r="K15" s="5"/>
+      <c r="N15" s="27"/>
+      <c r="O15" s="28" t="s">
+        <v>199</v>
+      </c>
+      <c r="P15" s="27"/>
+      <c r="Q15" s="12">
+        <v>12</v>
+      </c>
+      <c r="R15" s="12">
         <v>27</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="D14" s="12">
-        <v>11</v>
-      </c>
-      <c r="E14" s="12">
+      <c r="S15" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="T15" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="U15" s="5" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B16" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="E16" s="12">
+        <v>13</v>
+      </c>
+      <c r="F16" s="12">
         <v>26</v>
       </c>
-      <c r="N14" s="12">
-        <v>11</v>
-      </c>
-      <c r="O14" s="12">
+      <c r="G16" s="26" t="s">
+        <v>190</v>
+      </c>
+      <c r="H16" s="26" t="s">
+        <v>190</v>
+      </c>
+      <c r="I16" s="26" t="s">
+        <v>190</v>
+      </c>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+      <c r="N16" s="27"/>
+      <c r="O16" s="28" t="s">
+        <v>186</v>
+      </c>
+      <c r="P16" s="27"/>
+      <c r="Q16" s="12">
+        <v>13</v>
+      </c>
+      <c r="R16" s="12">
         <v>26</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="D15" s="12">
-        <v>12</v>
-      </c>
-      <c r="E15" s="7">
+      <c r="S16" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="T16" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="U16" s="5" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="17" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B17" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="E17" s="12">
+        <v>14</v>
+      </c>
+      <c r="F17" s="7">
         <v>25</v>
       </c>
-      <c r="N15" s="12">
-        <v>12</v>
-      </c>
-      <c r="O15" s="7">
+      <c r="G17" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="H17" s="27" t="s">
+        <v>226</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="J17" s="37" t="s">
+        <v>276</v>
+      </c>
+      <c r="K17" s="5"/>
+      <c r="N17" s="27"/>
+      <c r="O17" s="28" t="s">
+        <v>200</v>
+      </c>
+      <c r="P17" s="27"/>
+      <c r="Q17" s="12">
+        <v>14</v>
+      </c>
+      <c r="R17" s="7">
         <v>25</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="D16" s="12">
-        <v>13</v>
-      </c>
-      <c r="E16" s="7">
+      <c r="S17" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="T17" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="U17" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="18" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B18" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="E18" s="12">
+        <v>15</v>
+      </c>
+      <c r="F18" s="7">
         <v>24</v>
       </c>
-      <c r="N16" s="12">
-        <v>13</v>
-      </c>
-      <c r="O16" s="7">
+      <c r="G18" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="H18" s="27" t="s">
+        <v>227</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="J18" s="37" t="s">
+        <v>277</v>
+      </c>
+      <c r="K18" s="5"/>
+      <c r="N18" s="27"/>
+      <c r="O18" s="28" t="s">
+        <v>201</v>
+      </c>
+      <c r="P18" s="27"/>
+      <c r="Q18" s="12">
+        <v>15</v>
+      </c>
+      <c r="R18" s="7">
         <v>24</v>
       </c>
-    </row>
-    <row r="17" spans="4:15" x14ac:dyDescent="0.25">
-      <c r="D17" s="12">
-        <v>14</v>
-      </c>
-      <c r="E17" s="7">
+      <c r="S18" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="T18" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="U18" s="5" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="19" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B19" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="E19" s="12">
+        <v>16</v>
+      </c>
+      <c r="F19" s="7">
         <v>23</v>
       </c>
-      <c r="N17" s="12">
-        <v>14</v>
-      </c>
-      <c r="O17" s="7">
+      <c r="G19" s="27"/>
+      <c r="H19" s="27" t="s">
+        <v>228</v>
+      </c>
+      <c r="I19" s="27"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="5"/>
+      <c r="N19" s="27"/>
+      <c r="O19" s="28" t="s">
+        <v>202</v>
+      </c>
+      <c r="P19" s="27"/>
+      <c r="Q19" s="12">
+        <v>16</v>
+      </c>
+      <c r="R19" s="7">
         <v>23</v>
       </c>
-    </row>
-    <row r="18" spans="4:15" x14ac:dyDescent="0.25">
-      <c r="D18" s="12">
-        <v>15</v>
-      </c>
-      <c r="E18" s="7">
+      <c r="S19" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="T19" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="U19" s="7" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="20" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B20" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="E20" s="12">
+        <v>17</v>
+      </c>
+      <c r="F20" s="7">
         <v>22</v>
       </c>
-      <c r="N18" s="12">
-        <v>15</v>
-      </c>
-      <c r="O18" s="7">
+      <c r="G20" s="27"/>
+      <c r="H20" s="27" t="s">
+        <v>174</v>
+      </c>
+      <c r="I20" s="27"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="5"/>
+      <c r="N20" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="O20" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="P20" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="Q20" s="12">
+        <v>17</v>
+      </c>
+      <c r="R20" s="7">
         <v>22</v>
       </c>
-    </row>
-    <row r="19" spans="4:15" x14ac:dyDescent="0.25">
-      <c r="D19" s="12">
-        <v>16</v>
-      </c>
-      <c r="E19" s="7">
+      <c r="S20" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="T20" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="U20" s="5" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="21" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B21" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="E21" s="12">
+        <v>18</v>
+      </c>
+      <c r="F21" s="7">
         <v>21</v>
       </c>
-      <c r="N19" s="12">
-        <v>16</v>
-      </c>
-      <c r="O19" s="7">
+      <c r="G21" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="J21" s="5"/>
+      <c r="K21" s="5"/>
+      <c r="N21" s="27"/>
+      <c r="O21" s="28" t="s">
+        <v>207</v>
+      </c>
+      <c r="P21" s="27"/>
+      <c r="Q21" s="12">
+        <v>18</v>
+      </c>
+      <c r="R21" s="7">
         <v>21</v>
       </c>
-    </row>
-    <row r="20" spans="4:15" x14ac:dyDescent="0.25">
-      <c r="D20" s="12">
-        <v>17</v>
-      </c>
-      <c r="E20" s="7">
+      <c r="S21" s="26" t="s">
+        <v>190</v>
+      </c>
+      <c r="T21" s="26" t="s">
+        <v>190</v>
+      </c>
+      <c r="U21" s="26" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="22" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B22" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="E22" s="12">
+        <v>19</v>
+      </c>
+      <c r="F22" s="7">
         <v>20</v>
       </c>
-      <c r="N20" s="12">
-        <v>17</v>
-      </c>
-      <c r="O20" s="7">
+      <c r="G22" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="J22" s="5"/>
+      <c r="K22" s="5"/>
+      <c r="N22" s="27"/>
+      <c r="O22" s="28" t="s">
+        <v>208</v>
+      </c>
+      <c r="P22" s="27"/>
+      <c r="Q22" s="12">
+        <v>19</v>
+      </c>
+      <c r="R22" s="7">
         <v>20</v>
       </c>
-    </row>
-    <row r="21" spans="4:15" x14ac:dyDescent="0.25">
-      <c r="D21" s="12">
-        <v>18</v>
-      </c>
-      <c r="E21" s="7">
-        <v>19</v>
-      </c>
-      <c r="N21" s="12">
-        <v>18</v>
-      </c>
-      <c r="O21" s="7">
-        <v>19</v>
+      <c r="S22" s="26" t="s">
+        <v>190</v>
+      </c>
+      <c r="T22" s="26" t="s">
+        <v>190</v>
+      </c>
+      <c r="U22" s="26" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="27" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="K27" t="s">
+        <v>275</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="P2:R2"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="K2:M2"/>
+  <mergeCells count="3">
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="A1:V1"/>
+    <mergeCell ref="Q2:R2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3253,16 +4150,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
@@ -3363,13 +4260,13 @@
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="29" t="s">
+      <c r="A6" s="35" t="s">
         <v>106</v>
       </c>
-      <c r="B6" s="29" t="s">
+      <c r="B6" s="35" t="s">
         <v>112</v>
       </c>
-      <c r="C6" s="29" t="s">
+      <c r="C6" s="35" t="s">
         <v>86</v>
       </c>
       <c r="D6" s="12">
@@ -3378,29 +4275,29 @@
       <c r="E6" s="12">
         <v>13</v>
       </c>
-      <c r="F6" s="28" t="s">
+      <c r="F6" s="36" t="s">
         <v>86</v>
       </c>
-      <c r="G6" s="29" t="s">
+      <c r="G6" s="35" t="s">
         <v>112</v>
       </c>
-      <c r="H6" s="29" t="s">
+      <c r="H6" s="35" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="29"/>
-      <c r="B7" s="29"/>
-      <c r="C7" s="29"/>
+      <c r="A7" s="35"/>
+      <c r="B7" s="35"/>
+      <c r="C7" s="35"/>
       <c r="D7" s="12">
         <v>5</v>
       </c>
       <c r="E7" s="12">
         <v>12</v>
       </c>
-      <c r="F7" s="28"/>
-      <c r="G7" s="29"/>
-      <c r="H7" s="29"/>
+      <c r="F7" s="36"/>
+      <c r="G7" s="35"/>
+      <c r="H7" s="35"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
@@ -3498,16 +4395,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
@@ -3748,16 +4645,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
@@ -3786,7 +4683,7 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="26"/>
+      <c r="A3" s="32"/>
       <c r="B3" s="5"/>
       <c r="C3" s="5" t="s">
         <v>88</v>
@@ -3801,10 +4698,10 @@
         <v>101</v>
       </c>
       <c r="G3" s="5"/>
-      <c r="H3" s="26"/>
+      <c r="H3" s="32"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="26"/>
+      <c r="A4" s="32"/>
       <c r="B4" s="5"/>
       <c r="C4" s="8" t="s">
         <v>94</v>
@@ -3819,10 +4716,10 @@
         <v>100</v>
       </c>
       <c r="G4" s="5"/>
-      <c r="H4" s="26"/>
+      <c r="H4" s="32"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="26"/>
+      <c r="A5" s="32"/>
       <c r="B5" s="5"/>
       <c r="C5" s="8" t="s">
         <v>93</v>
@@ -3837,7 +4734,7 @@
         <v>99</v>
       </c>
       <c r="G5" s="5"/>
-      <c r="H5" s="26"/>
+      <c r="H5" s="32"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
@@ -3866,7 +4763,7 @@
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="26"/>
+      <c r="A7" s="32"/>
       <c r="B7" s="5"/>
       <c r="C7" s="8" t="s">
         <v>91</v>
@@ -3881,10 +4778,10 @@
         <v>98</v>
       </c>
       <c r="G7" s="5"/>
-      <c r="H7" s="26"/>
+      <c r="H7" s="32"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="26"/>
+      <c r="A8" s="32"/>
       <c r="B8" s="5"/>
       <c r="C8" s="8" t="s">
         <v>92</v>
@@ -3899,10 +4796,10 @@
         <v>97</v>
       </c>
       <c r="G8" s="5"/>
-      <c r="H8" s="26"/>
+      <c r="H8" s="32"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="26"/>
+      <c r="A9" s="32"/>
       <c r="B9" s="5"/>
       <c r="C9" s="5" t="s">
         <v>89</v>
@@ -3917,7 +4814,7 @@
         <v>90</v>
       </c>
       <c r="G9" s="5"/>
-      <c r="H9" s="26"/>
+      <c r="H9" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="5">
